--- a/examples/jpetstore-6/.understand-anything/doc-output/si-위험모듈리포트.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-위험모듈리포트.xlsx
@@ -158,7 +158,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
   </cols>
@@ -198,7 +198,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>순환복잡도 근사(java AST): 메서드 수 + 결정포인트(if/for/while/do/catch/삼항/case/&amp;&amp;/||). 비 java 는 미측정 [미확인]</t>
+          <t>순환복잡도 근사(java AST): 메서드 수 + 결정포인트(if/for/while/do/catch/삼항/case/&amp;&amp;/||). 비 java 는 미측정 [미확인] — 백분위는 측정(java) 집합 내 순위</t>
         </is>
       </c>
       <c r="C2">
@@ -219,7 +219,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>git 전체 이력에서 파일별 변경 커밋 수(git log --numstat, rename 미추적). 변경 라인은 참고치</t>
+          <t>git 전체 이력에서 파일별 변경 커밋 수(git log --numstat, rename 미추적·shallow clone 은 미측정 처리). 변경 라인은 참고치</t>
         </is>
       </c>
       <c r="C3">
@@ -303,11 +303,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>진입점(라우트·배치)에서 도달 불가 여부(slices 도달성 — 이진)</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>0.1</v>
+          <t>진입점(라우트·배치)에서 도달 불가 여부(slices 도달성 — 이진). 점수 비반영 플래그: 뷰 forward(JSP 등) 미추적 한계로 오탐 가능 — 데드코드 판정은 사람 확인</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>플래그(비점수)</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -324,7 +326,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>지표별 프로젝트 내 백분위(0~1, 동점 평균) → 가중 합산. 미측정 지표는 가중치 재정규화(미측정 파일 과소평가 방지). 점수는 프로젝트 내 상대 순위이며 절대 품질 판정이 아님</t>
+          <t>지표별 프로젝트 내 백분위(0~1, 동점 평균) → 가중 합산(가중치는 휴리스틱 — 점수는 순위로만 해석). 미측정 지표는 가중치 재정규화(미측정 파일 과소평가 방지), 무분산 지표(전 파일 동일값)는 변별 기여가 없어 제외. 점수는 프로젝트 내 상대 순위이며 절대 품질 판정이 아님</t>
         </is>
       </c>
       <c r="C8"/>
@@ -343,7 +345,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>상 ≥ 0.66 · 중 ≥ 0.33 · 하 &lt; 0.33 (고정 임계)</t>
+          <t>프로젝트 내 상대 밴드 — 상 = 점수 상위 10%(최소 1본, 동점 상향) · 중 = 상위 30% · 하 = 나머지. 절대 품질 판정 아님</t>
         </is>
       </c>
       <c r="C9"/>
@@ -364,7 +366,7 @@
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="9" customWidth="1"/>
@@ -487,7 +489,7 @@
         </is>
       </c>
       <c r="F2">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -551,11 +553,11 @@
         </is>
       </c>
       <c r="F3">
-        <v>0.65</v>
+        <v>0.81</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
       <c r="H3">
@@ -615,11 +617,11 @@
         </is>
       </c>
       <c r="F4">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
       <c r="H4">
@@ -679,11 +681,11 @@
         </is>
       </c>
       <c r="F5">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
       <c r="H5">
@@ -743,11 +745,11 @@
         </is>
       </c>
       <c r="F6">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
       <c r="H6">
@@ -807,11 +809,11 @@
         </is>
       </c>
       <c r="F7">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
       <c r="H7">
@@ -871,7 +873,7 @@
         </is>
       </c>
       <c r="F8">
-        <v>0.60</v>
+        <v>0.73</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -935,7 +937,7 @@
         </is>
       </c>
       <c r="F9">
-        <v>0.60</v>
+        <v>0.73</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -980,57 +982,51 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PGM-SCR-dbbf9812</t>
+          <t>PGM-SVC-d564b236</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ViewOrder</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>web-inf</t>
+          <t>order</t>
         </is>
       </c>
       <c r="F10">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[미확인]</t>
-        </is>
+      <c r="H10">
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>미도달</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="M10"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>미도달, LOC</t>
+          <t>팬아웃, LOC</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1040,7 +1036,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/order/ViewOrder.jsp:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/service/OrderService.java:1</t>
         </is>
       </c>
     </row>
@@ -1050,17 +1046,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PGM-SVC-d564b236</t>
+          <t>PGM-COM-b6277a61</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>LineItem</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>공통/기타</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1069,7 +1065,7 @@
         </is>
       </c>
       <c r="F11">
-        <v>0.56</v>
+        <v>0.63</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1077,19 +1073,19 @@
         </is>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I11">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
       <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
         <v>2</v>
-      </c>
-      <c r="L11">
-        <v>4</v>
       </c>
       <c r="M11"/>
       <c r="N11" t="inlineStr">
@@ -1104,7 +1100,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>src/main/java/org/mybatis/jpetstore/service/OrderService.java:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/domain/LineItem.java:1</t>
         </is>
       </c>
     </row>
@@ -1114,26 +1110,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PGM-SCR-9a011004</t>
+          <t>PGM-MAP-19fe2f40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IncludeTop</t>
+          <t>AccountMapper</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>SQL매퍼</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>web-inf</t>
+          <t>account</t>
         </is>
       </c>
       <c r="F12">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1146,35 +1142,31 @@
         </is>
       </c>
       <c r="I12">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>미도달</t>
-        </is>
-      </c>
+      <c r="M12"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>미도달, LOC</t>
+          <t>LOC, 팬인</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>[확정]</t>
+          <t>[추정]</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/common/IncludeTop.jsp:1</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:1</t>
         </is>
       </c>
     </row>
@@ -1184,57 +1176,51 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PGM-SCR-ed0c6c14</t>
+          <t>PGM-COM-51c62df1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ConfirmOrder</t>
+          <t>Cart</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>공통/기타</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>web-inf</t>
+          <t>cart</t>
         </is>
       </c>
       <c r="F13">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>[미확인]</t>
-        </is>
+      <c r="H13">
+        <v>12</v>
       </c>
       <c r="I13">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>미도달</t>
-        </is>
-      </c>
+      <c r="M13"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>미도달, LOC</t>
+          <t>LOC, 복잡도</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1244,7 +1230,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/order/ConfirmOrder.jsp:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/domain/Cart.java:1</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1240,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PGM-COM-b6277a61</t>
+          <t>PGM-COM-9f4f6427</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LineItem</t>
+          <t>CartItem</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1269,11 +1255,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>order</t>
+          <t>cart+order</t>
         </is>
       </c>
       <c r="F14">
-        <v>0.54</v>
+        <v>0.60</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1281,24 +1267,24 @@
         </is>
       </c>
       <c r="H14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>팬아웃, LOC</t>
+          <t>팬아웃, 팬인</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1308,7 +1294,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>src/main/java/org/mybatis/jpetstore/domain/LineItem.java:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/domain/CartItem.java:1</t>
         </is>
       </c>
     </row>
@@ -1318,26 +1304,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PGM-SCR-3c93f7f6</t>
+          <t>PGM-MAP-d1be15e8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cart</t>
+          <t>OrderMapper</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>SQL매퍼</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>web-inf</t>
+          <t>order</t>
         </is>
       </c>
       <c r="F15">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1350,35 +1336,31 @@
         </is>
       </c>
       <c r="I15">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>미도달</t>
-        </is>
-      </c>
+      <c r="M15"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>미도달, LOC</t>
+          <t>LOC, 팬인</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>[확정]</t>
+          <t>[추정]</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/cart/Cart.jsp:1</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:1</t>
         </is>
       </c>
     </row>
@@ -1388,26 +1370,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PGM-COM-51c62df1</t>
+          <t>PGM-DAO-51f037a7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cart</t>
+          <t>AccountMapper</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>공통/기타</t>
+          <t>DAO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>cart</t>
+          <t>account</t>
         </is>
       </c>
       <c r="F16">
-        <v>0.53</v>
+        <v>0.56</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1415,24 +1397,24 @@
         </is>
       </c>
       <c r="H16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>LOC, 복잡도</t>
+          <t>팬인, 팬아웃</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1442,7 +1424,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>src/main/java/org/mybatis/jpetstore/domain/Cart.java:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/mapper/AccountMapper.java:1</t>
         </is>
       </c>
     </row>
@@ -1452,57 +1434,51 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PGM-SCR-b1ada8ee</t>
+          <t>PGM-COM-f9a3f312</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>공통/기타</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>web-inf</t>
+          <t>account+cart+catalog+order</t>
         </is>
       </c>
       <c r="F17">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>[미확인]</t>
-        </is>
+      <c r="H17">
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="J17">
         <v>1</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>미도달</t>
-        </is>
-      </c>
+      <c r="M17"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>미도달, LOC</t>
+          <t>팬인, 복잡도</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1512,7 +1488,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/catalog/Main.jsp:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/domain/Product.java:1</t>
         </is>
       </c>
     </row>
@@ -1522,30 +1498,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PGM-SCR-26b9e12b</t>
+          <t>PGM-MAP-81a3e7d5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NewOrderForm</t>
+          <t>ItemMapper</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>SQL매퍼</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>web-inf</t>
+          <t>account+cart+catalog+order</t>
         </is>
       </c>
       <c r="F18">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1554,35 +1530,31 @@
         </is>
       </c>
       <c r="I18">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>미도달</t>
-        </is>
-      </c>
+      <c r="M18"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>미도달, LOC</t>
+          <t>팬인, LOC</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>[확정]</t>
+          <t>[추정]</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/order/NewOrderForm.jsp:1</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:1</t>
         </is>
       </c>
     </row>
@@ -1592,57 +1564,51 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PGM-SCR-17377901</t>
+          <t>PGM-SVC-5f5bf3cb</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IncludeAccountFields</t>
+          <t>AccountService</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>web-inf</t>
+          <t>account</t>
         </is>
       </c>
       <c r="F19">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>[미확인]</t>
-        </is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="H19">
+        <v>5</v>
       </c>
       <c r="I19">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J19">
         <v>1</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>미도달</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M19"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>미도달, LOC</t>
+          <t>팬인, 팬아웃</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1652,7 +1618,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/account/IncludeAccountFields.jsp:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/service/AccountService.java:1</t>
         </is>
       </c>
     </row>
@@ -1662,61 +1628,67 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PGM-COM-9f4f6427</t>
+          <t>PGM-SCR-dbbf9812</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CartItem</t>
+          <t>ViewOrder</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>공통/기타</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>cart+order</t>
+          <t>web-inf</t>
         </is>
       </c>
       <c r="F20">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="H20">
-        <v>9</v>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[미확인]</t>
+        </is>
       </c>
       <c r="I20">
-        <v>76</v>
+        <v>173</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20"/>
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>미도달</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>팬아웃, 팬인</t>
+          <t>LOC, 팬아웃</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>[확정]</t>
+          <t>[추정]</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>src/main/java/org/mybatis/jpetstore/domain/CartItem.java:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/order/ViewOrder.jsp:1</t>
         </is>
       </c>
     </row>
@@ -1726,57 +1698,51 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PGM-SCR-807f6244</t>
+          <t>PGM-DAO-867b6414</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>ItemMapper</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>DAO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>web-inf</t>
+          <t>account+cart+catalog+order</t>
         </is>
       </c>
       <c r="F21">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[미확인]</t>
-        </is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="H21">
+        <v>4</v>
       </c>
       <c r="I21">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="J21">
         <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>미도달</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M21"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>미도달, LOC</t>
+          <t>팬인, 팬아웃</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1786,7 +1752,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/catalog/Product.jsp:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/mapper/ItemMapper.java:1</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1765,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
@@ -1877,17 +1843,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>복잡도 측정</t>
+          <t>등급 분포</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24/52</t>
+          <t>상 6 · 중 10 · 하 36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>미측정 = 비 java(jsp·SQL매퍼 등) — [미확인]</t>
+          <t>상대 밴드(상위 10%/30%) — 절대 판정 아님</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1900,17 +1866,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>변경빈도 측정</t>
+          <t>복잡도 측정</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>52/52</t>
+          <t>24/52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>git 이력 기준(앵커 e31bb89b17bf339d0c8f6512d5f4ed0c6c0cebd4)</t>
+          <t>미측정(확장자별): jsp 20, xml 8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1923,25 +1889,73 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>변경빈도 측정</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>52/52</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>git 이력 기준(앵커 c64558efee7bc7e149d24ec73ce39a1d5f7ba44e)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[추정]</t>
+        </is>
+      </c>
+      <c r="E6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>무분산 지표</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>변경빈도</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>전 파일 동일값 — 랭킹 변별 기여 없음(가중합 제외). 예: 단일 벤더링 커밋의 변경빈도</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[추정]</t>
+        </is>
+      </c>
+      <c r="E7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>미도달</t>
         </is>
       </c>
-      <c r="B6">
-        <v>20</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>진입점에서 도달 불가(데드코드 후보)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20/52</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>점수 비반영 플래그 — 뷰 forward(JSP) 미추적 한계로 오탐 가능, 데드코드 판정은 사람 확인</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>[추정]</t>
         </is>
       </c>
-      <c r="E6"/>
+      <c r="E8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:E8"/>
 </worksheet>
 </file>
--- a/examples/jpetstore-6/.understand-anything/doc-output/si-위험모듈리포트.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-위험모듈리포트.xlsx
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>git 이력 기준(앵커 c64558efee7bc7e149d24ec73ce39a1d5f7ba44e)</t>
+          <t>git 이력 기준(앵커 dfbb9822f7c17f41a39e96704f4ea4f455580278)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/examples/jpetstore-6/.understand-anything/doc-output/si-위험모듈리포트.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-위험모듈리포트.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>dfbb9822f7c17f41a39e96704f4ea4f455580278</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>web-inf</t>
+          <t>order</t>
         </is>
       </c>
       <c r="F20">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>git 이력 기준(앵커 dfbb9822f7c17f41a39e96704f4ea4f455580278)</t>
+          <t>git 이력 기준(앵커 d51826fcf3b5618e4a5fc6f5fa1657de3c390ad6)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
